--- a/ig/StructureDefinition-as-codeableconcept-timed.xlsx
+++ b/ig/StructureDefinition-as-codeableconcept-timed.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="287" uniqueCount="130">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="287" uniqueCount="129">
   <si>
     <t>Property</t>
   </si>
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.0.0-ballot-4</t>
+    <t>1.0.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-03T14:12:51+00:00</t>
+    <t>2024-04-10T13:25:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -69,7 +69,7 @@
     <t>Contact</t>
   </si>
   <si>
-    <t>No display for ContactDetail</t>
+    <t>Agence du Numérique en Santé (ANS) - 2-10 Rue d'Oradour-sur-Glane, 75015 Paris (https://esante.gouv.fr, monserviceclient.annuaire@esante.gouv.fr)</t>
   </si>
   <si>
     <t>Jurisdiction</t>
@@ -339,9 +339,6 @@
   <si>
     <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
 ext-1:Must have either extensions or value[x], not both {extension.exists() != value.exists()}</t>
-  </si>
-  <si>
-    <t>N/A</t>
   </si>
   <si>
     <t>CodeableConcept.extension:as-codeableconcept-timed-metadata</t>
@@ -1192,7 +1189,7 @@
         <v>78</v>
       </c>
       <c r="AI4" t="s" s="2">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="AJ4" t="s" s="2">
         <v>105</v>
@@ -1201,7 +1198,7 @@
         <v>76</v>
       </c>
       <c r="AL4" t="s" s="2">
-        <v>106</v>
+        <v>94</v>
       </c>
       <c r="AM4" t="s" s="2">
         <v>76</v>
@@ -1209,13 +1206,13 @@
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B5" t="s" s="2">
         <v>95</v>
       </c>
       <c r="C5" t="s" s="2">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="D5" t="s" s="2">
         <v>76</v>
@@ -1237,13 +1234,13 @@
         <v>76</v>
       </c>
       <c r="K5" t="s" s="2">
+        <v>108</v>
+      </c>
+      <c r="L5" t="s" s="2">
         <v>109</v>
       </c>
-      <c r="L5" t="s" s="2">
+      <c r="M5" t="s" s="2">
         <v>110</v>
-      </c>
-      <c r="M5" t="s" s="2">
-        <v>111</v>
       </c>
       <c r="N5" s="2"/>
       <c r="O5" s="2"/>
@@ -1303,7 +1300,7 @@
         <v>78</v>
       </c>
       <c r="AI5" t="s" s="2">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="AJ5" t="s" s="2">
         <v>105</v>
@@ -1320,10 +1317,10 @@
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="C6" s="2"/>
       <c r="D6" t="s" s="2">
@@ -1343,22 +1340,22 @@
         <v>76</v>
       </c>
       <c r="J6" t="s" s="2">
+        <v>112</v>
+      </c>
+      <c r="K6" t="s" s="2">
         <v>113</v>
       </c>
-      <c r="K6" t="s" s="2">
+      <c r="L6" t="s" s="2">
         <v>114</v>
       </c>
-      <c r="L6" t="s" s="2">
+      <c r="M6" t="s" s="2">
         <v>115</v>
       </c>
-      <c r="M6" t="s" s="2">
+      <c r="N6" t="s" s="2">
         <v>116</v>
       </c>
-      <c r="N6" t="s" s="2">
+      <c r="O6" t="s" s="2">
         <v>117</v>
-      </c>
-      <c r="O6" t="s" s="2">
-        <v>118</v>
       </c>
       <c r="P6" t="s" s="2">
         <v>76</v>
@@ -1407,7 +1404,7 @@
         <v>76</v>
       </c>
       <c r="AF6" t="s" s="2">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="AG6" t="s" s="2">
         <v>77</v>
@@ -1416,27 +1413,27 @@
         <v>78</v>
       </c>
       <c r="AI6" t="s" s="2">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="AJ6" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AK6" t="s" s="2">
+        <v>118</v>
+      </c>
+      <c r="AL6" t="s" s="2">
         <v>119</v>
       </c>
-      <c r="AL6" t="s" s="2">
+      <c r="AM6" t="s" s="2">
         <v>120</v>
-      </c>
-      <c r="AM6" t="s" s="2">
-        <v>121</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C7" s="2"/>
       <c r="D7" t="s" s="2">
@@ -1456,22 +1453,22 @@
         <v>76</v>
       </c>
       <c r="J7" t="s" s="2">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="K7" t="s" s="2">
         <v>90</v>
       </c>
       <c r="L7" t="s" s="2">
+        <v>122</v>
+      </c>
+      <c r="M7" t="s" s="2">
         <v>123</v>
       </c>
-      <c r="M7" t="s" s="2">
+      <c r="N7" t="s" s="2">
         <v>124</v>
       </c>
-      <c r="N7" t="s" s="2">
+      <c r="O7" t="s" s="2">
         <v>125</v>
-      </c>
-      <c r="O7" t="s" s="2">
-        <v>126</v>
       </c>
       <c r="P7" t="s" s="2">
         <v>76</v>
@@ -1520,7 +1517,7 @@
         <v>76</v>
       </c>
       <c r="AF7" t="s" s="2">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="AG7" t="s" s="2">
         <v>77</v>
@@ -1529,19 +1526,19 @@
         <v>89</v>
       </c>
       <c r="AI7" t="s" s="2">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="AJ7" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AK7" t="s" s="2">
+        <v>126</v>
+      </c>
+      <c r="AL7" t="s" s="2">
         <v>127</v>
       </c>
-      <c r="AL7" t="s" s="2">
+      <c r="AM7" t="s" s="2">
         <v>128</v>
-      </c>
-      <c r="AM7" t="s" s="2">
-        <v>129</v>
       </c>
     </row>
   </sheetData>

--- a/ig/StructureDefinition-as-codeableconcept-timed.xlsx
+++ b/ig/StructureDefinition-as-codeableconcept-timed.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.0.0</t>
+    <t>1.0.1</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-10T13:25:16+00:00</t>
+    <t>2024-04-25T11:50:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/StructureDefinition-as-codeableconcept-timed.xlsx
+++ b/ig/StructureDefinition-as-codeableconcept-timed.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-25T11:50:43+00:00</t>
+    <t>2024-04-26T07:42:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
